--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T09:04:28+00:00</t>
+    <t>2024-10-26T11:58:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T11:58:28+00:00</t>
+    <t>2024-10-26T12:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:16:12+00:00</t>
+    <t>2024-10-26T12:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:32:55+00:00</t>
+    <t>2024-10-26T13:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:09:27+00:00</t>
+    <t>2024-10-26T13:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:28:10+00:00</t>
+    <t>2024-10-26T14:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T14:16:20+00:00</t>
+    <t>2024-10-26T14:33:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T14:33:31+00:00</t>
+    <t>2024-10-30T15:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T15:48:47+00:00</t>
+    <t>2024-11-17T20:47:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:47:41+00:00</t>
+    <t>2024-11-17T21:11:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:11:32+00:00</t>
+    <t>2024-11-17T21:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:35:06+00:00</t>
+    <t>2024-11-27T13:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-27T13:18:58+00:00</t>
+    <t>2024-12-15T14:03:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-15T14:03:14+00:00</t>
+    <t>2024-12-19T08:32:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="257">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-19T08:32:44+00:00</t>
+    <t>2025-01-08T14:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -725,19 +725,13 @@
 </t>
   </si>
   <si>
-    <t>Contact information</t>
-  </si>
-  <si>
-    <t>Specifies contact information for a specific purpose over a period of time, might be handled/monitored by a specific named person or organization.</t>
-  </si>
-  <si>
-    <t>This datatype may be sparsely populated, i.e. only contain a purpose and phone number or address, but other cases could be completed filled out.</t>
+    <t>Official contact details relating to this PractitionerRole</t>
+  </si>
+  <si>
+    <t>The contact details of communication devices available relevant to the specific PractitionerRole. This can include addresses, phone numbers, fax numbers, mobile numbers, email addresses and web sites.</t>
   </si>
   <si>
     <t>Often practitioners have a dedicated line for each location (or service) that they work at, and need to be able to define separate contact details for each of these. Sometimes these also include a named person/organization that handles contact for specific purposes, such as a receptionist, or accounts clerk etc.</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>PractitionerRole.characteristic</t>
@@ -821,6 +815,9 @@
   <si>
     <t>Organizations have multiple systems that provide various services and may also be different for practitioners too.
 So the endpoint satisfies the need to be able to define the technical connection details for how to connect to them, and for what purpose.</t>
+  </si>
+  <si>
+    <t>n/a</t>
   </si>
 </sst>
 </file>
@@ -3440,11 +3437,9 @@
       <c r="M20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="N20" s="2"/>
+      <c r="O20" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3514,7 +3509,7 @@
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -3525,10 +3520,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3554,13 +3549,13 @@
         <v>193</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3586,14 +3581,14 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Z21" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="Y21" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
       </c>
@@ -3610,7 +3605,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3631,7 +3626,7 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
@@ -3642,10 +3637,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3671,16 +3666,16 @@
         <v>193</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3729,7 +3724,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3750,7 +3745,7 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -3761,10 +3756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3787,16 +3782,16 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3846,7 +3841,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3867,7 +3862,7 @@
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
@@ -3878,10 +3873,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3904,17 +3899,17 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -3963,7 +3958,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3984,7 +3979,7 @@
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T14:32:12+00:00</t>
+    <t>2025-01-24T13:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T13:05:30+00:00</t>
+    <t>2025-01-24T15:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T15:13:16+00:00</t>
+    <t>2025-01-27T12:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T09:10:20+00:00</t>
+    <t>2026-03-01T19:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:31:53+00:00</t>
+    <t>2026-07-17T05:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
